--- a/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_30_tokens_0.1_temp_factual_retrieval_raw_table_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_30_tokens_0.1_temp_factual_retrieval_raw_table_08-24-4.xlsx
@@ -494,24 +494,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China.
+The Great Wall of China is located in China.
+The Great Wall of China is located in China</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 0.5), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -532,24 +535,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China. It is located in the northern part of China. It is located in the northern part of China</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -570,24 +574,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China.
+The Great Wall of China is located in China.
+The Great Wall of China is located in China</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 0.5), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -608,24 +615,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China. It is located in the northern part of China. It is located in the northern part of China</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -646,24 +654,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China.
+The Great Wall of China is located in China.
+The Great Wall of China is located in China</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 0.5), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -684,24 +695,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China.
+The Great Wall of China is located in China.
+The Great Wall of China is located in China</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 0.5), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -722,24 +736,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China.
+The Great Wall of China is located in China.
+The Great Wall of China is located in China</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 0.5), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -760,24 +777,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China.
+The Great Wall of China is located in China.
+The Great Wall of China is located in China</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 0.5), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -798,24 +818,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China.
+The Great Wall of China is located in China.
+The Great Wall of China is located in China</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 0.5), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -836,24 +859,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China.
+The Great Wall of China is located in China.
+The Great Wall of China is located in China</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G11" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 0.5), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -874,24 +900,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France.
+The Eiffel Tower is located in Paris, France.
+The Eiffel Tower</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9434345960617065</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.\n', 0.5), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0)]</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -912,24 +941,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a large park in the 7th arr</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France. The Eiffel Tower is located in Paris, France. The Eiffel Tower</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>0.0607767142355442</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9108731746673584</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.081308841705322</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' large', 1.0), (' park', 1.0), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 0.5), (' The', 0.3486), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0)]</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -950,24 +980,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France.
+The Eiffel Tower is located in Paris, France.
+The Eiffel Tower</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9434345960617065</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.\n', 0.5), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0)]</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -988,24 +1021,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a large park in the 7th arr</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France.
+The Eiffel Tower is located in Paris, France.
+The Eiffel Tower</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.5</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9434345960617065</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' large', 1.0), (' park', 1.0), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.\n', 0.5), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0)]</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1026,24 +1062,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a large park in the 7th arr</t>
+          <t>Where is the Eiffel Tower located???
+A. In Paris, France
+B. In New York City, USA
+C. In London, England
+D. In Tokyo, Japan</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.5</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9517875909805298</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' large', 1.0), (' park', 1.0), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' In', 0.3486), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' In', 1.0), (' New', 1.0), (' York', 1.0), (' City', 1.0), (',', 1.0), (' USA', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' In', 1.0), (' London', 1.0), (',', 1.0), (' England', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' In', 1.0), (' Tokyo', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1064,24 +1104,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+A. In Paris, France
+B. In New York City, USA
+C. In London, England
+D. In Tokyo, Japan</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9517875909805298</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' In', 0.3486), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' In', 1.0), (' New', 1.0), (' York', 1.0), (' City', 1.0), (',', 1.0), (' USA', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' In', 1.0), (' London', 1.0), (',', 1.0), (' England', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' In', 1.0), (' Tokyo', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1102,24 +1146,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a large park in the 7th arr</t>
+          <t>Where is the Eiffel Tower located???
+A. In Paris, France
+B. In New York City, USA
+C. In London, England
+D. In Tokyo, Japan</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9517875909805298</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' large', 1.0), (' park', 1.0), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' In', 0.3486), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' In', 1.0), (' New', 1.0), (' York', 1.0), (' City', 1.0), (',', 1.0), (' USA', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' In', 1.0), (' London', 1.0), (',', 1.0), (' England', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' In', 1.0), (' Tokyo', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1140,24 +1188,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+A. Paris, France
+B. New York, USA
+C. London, England
+D. Tokyo, Japan
+E. Moscow,</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5</v>
+        <v>0.07395864278078079</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9168528318405151</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.272413611412048</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Paris', 0.6514), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' New', 1.0), (' York', 1.0), (',', 0.5), (' USA', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' London', 1.0), (',', 1.0), (' England', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Tokyo', 1.0), (',', 1.0), (' Japan', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Moscow', 0.3486), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1178,24 +1231,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+A. Paris, France
+B. New York City, USA
+C. London, England
+D. Tokyo, Japan
+E. Rome</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5</v>
+        <v>0.1381729543209076</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.936154305934906</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.184282183647156</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Paris', 0.6514), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' New', 1.0), (' York', 1.0), (' City', 0.5), (',', 1.0), (' USA', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' London', 1.0), (',', 1.0), (' England', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Tokyo', 1.0), (',', 1.0), (' Japan', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Rome', 0.6514)]</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1216,24 +1274,29 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+A. Paris, France
+B. New York, USA
+C. London, England
+D. Tokyo, Japan
+E. Rome,</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5</v>
+        <v>0.1381729543209076</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.936154305934906</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.184282183647156</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Paris', 0.6514), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' New', 1.0), (' York', 1.0), (',', 0.5), (' USA', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' London', 1.0), (',', 1.0), (' England', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Tokyo', 1.0), (',', 1.0), (' Japan', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Rome', 0.6514), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1254,24 +1317,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu, and is the largest</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.3020975589752197</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9608853459358215</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.7382223606109619</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), (',', 0.5), (' and', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 0.7773)]</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1292,24 +1356,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. It is the largest</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.3020975589752197</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9608853459358215</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.7382223606109619</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 0.5), (' It', 0.7773), (' is', 1.0), (' the', 1.0), (' largest', 1.0)]</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1330,24 +1395,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on the island</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu, and is the largest</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.3020975589752197</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9608853459358215</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.7382223606109619</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), (',', 0.5), (' and', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 0.7773)]</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1368,24 +1434,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on the island</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu, and is the largest</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.3020975589752197</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9608853459358215</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.7382223606109619</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), (',', 0.5), (' and', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 0.7773)]</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1406,24 +1473,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. It is the largest</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.3020975589752197</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9608853459358215</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.7382223606109619</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 0.5), (' It', 0.7773), (' is', 1.0), (' the', 1.0), (' largest', 1.0)]</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1444,24 +1512,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu, and is the largest</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.3020975589752197</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9608853459358215</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.7382223606109619</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), (',', 0.5), (' and', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 0.7773)]</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1482,24 +1551,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. It is the largest</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.3020975589752197</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9608853459358215</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.7382223606109619</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 0.5), (' It', 0.7773), (' is', 1.0), (' the', 1.0), (' largest', 1.0)]</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1520,24 +1590,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+The answer is Tokyo. Tokyo is the capital city of Japan. Tokyo is the largest city in Japan and the largest metropolitan area in the world.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.02528667822480202</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.8846328258514404</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5423979759216309</v>
+        <v>1.327657222747803</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.2227), (' answer', 0.6514), (' is', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' Tokyo', 0.3486), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' Tokyo', 0.5), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1558,24 +1629,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on the island</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu, and is the most</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.08655239641666412</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9216710925102234</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.8768777847290039</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), (',', 0.5), (' and', 1.0), (' is', 1.0), (' the', 1.0), (' most', 0.2227)]</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -1596,24 +1668,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on the island</t>
+          <t>What is the capital city of Japan???
+The capital city of Japan is Tokyo. Tokyo is the largest city in the world. It is also the most populous city in the world. Tokyo</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.009591827169060707</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.856505274772644</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5423979759216309</v>
+        <v>1.878796100616455</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.2227), (' capital', 0.3486), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.', 0.5), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 0.6357), (' It', 1.0), (' is', 1.0), (' also', 0.7773), (' the', 1.0), (' most', 0.5), (' populous', 1.0), (' city', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0)]</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -1634,28 +1707,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+The answer is: It depends on the person.
+The taste of a lemon is a subjective experience. It is based on the person’s taste buds</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.007544020190834999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.8496761322021484</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5423979759216309</v>
+        <v>1.937392592430115</v>
       </c>
       <c r="H32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.5), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('.\n', 0.5), ('The', 1.0), (' taste', 0.3486), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' a', 1.0), (' subjective', 1.0), (' experience', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' based', 0.2227), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('’s', 1.0), (' taste', 0.7773), (' buds', 1.0)]</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="33">
@@ -1672,28 +1747,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as sour and bitter. I would describe the taste of a lemon as sour and bitter.
+I would describe</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.5), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0)]</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="34">
@@ -1710,28 +1787,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? What about the sound of a bird singing? What about the feeling of a warm summer breeze? What about the</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as sour and bitter. I would describe the taste of a lemon as sour and bitter.
+I would describe</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.01941082999110222</v>
+        <v>0.5</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8768692016601562</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G34" t="n">
-        <v>1.394994616508484</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' What', 0.3486), (' about', 1.0), (' the', 1.0), (' sound', 1.0), (' of', 1.0), (' a', 1.0), (' bird', 1.0), (' singing', 0.5), ('?', 1.0), (' What', 1.0), (' about', 1.0), (' the', 1.0), (' feeling', 0.5), (' of', 1.0), (' a', 1.0), (' warm', 1.0), (' summer', 1.0), (' breeze', 1.0), ('?', 1.0), (' What', 1.0), (' about', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.5), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0)]</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="35">
@@ -1748,28 +1827,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+The answer is: It depends on the person.
+The same is true for the taste of a wine. It depends on the person. The same</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.05303289368748665</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9067443013191223</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5423979759216309</v>
+        <v>1.598193168640137</v>
       </c>
       <c r="H35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.5), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('.\n', 0.5), ('The', 1.0), (' same', 0.6514), (' is', 1.0), (' true', 1.0), (' for', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' wine', 1.0), ('.', 1.0), (' It', 1.0), (' depends', 1.0), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('.', 1.0), (' The', 1.0), (' same', 0.6514)]</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="36">
@@ -1786,28 +1867,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+The answer is: It is sour.
+The question is: How would you describe the taste of a lemon???
+The answer is: It is</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.25</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.5), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' is', 0.5), (' sour', 1.0), ('.\n', 1.0), ('The', 1.0), (' question', 1.0), (' is', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="37">
@@ -1824,28 +1908,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+The answer is: It depends on the person.
+The taste of a lemon is a subjective experience. It is not a fact. It is not</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.01693761348724365</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.8728944659233093</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5423979759216309</v>
+        <v>1.949486374855042</v>
       </c>
       <c r="H37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.5), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('.\n', 0.5), ('The', 1.0), (' taste', 0.3486), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' a', 1.0), (' subjective', 1.0), (' experience', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' not', 0.7773), (' a', 0.5), (' fact', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' not', 1.0)]</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="38">
@@ -1862,28 +1948,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it hot? Is it cold? Is it</t>
+          <t>How would you describe the taste of a lemon???
+The answer is: It is sour.
+The question is: How would you describe the taste of a lemon???
+The answer is: It is</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.25</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' hot', 0.5), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' cold', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.5), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' is', 0.5), (' sour', 1.0), ('.\n', 1.0), ('The', 1.0), (' question', 1.0), (' is', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="39">
@@ -1900,28 +1989,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? What about the sound of a bird chirping? These are all examples of sensory experiences that we can describe,</t>
+          <t>How would you describe the taste of a lemon???
+The answer is: It depends on the person.
+The same is true for the taste of a wine. It depends on the person. The same</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.01941082999110222</v>
+        <v>0.05303289368748665</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8768692016601562</v>
+        <v>0.9067443013191223</v>
       </c>
       <c r="G39" t="n">
-        <v>1.394994616508484</v>
+        <v>1.598193168640137</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' What', 0.3486), (' about', 1.0), (' the', 1.0), (' sound', 1.0), (' of', 1.0), (' a', 1.0), (' bird', 1.0), (' chir', 0.5), ('ping', 1.0), ('?', 1.0), (' These', 1.0), (' are', 1.0), (' all', 1.0), (' examples', 1.0), (' of', 1.0), (' sensory', 1.0), (' experiences', 1.0), (' that', 1.0), (' we', 1.0), (' can', 1.0), (' describe', 1.0), (',', 0.5)]</t>
+          <t>[('?\n', 1.0), ('The', 0.5), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('.\n', 0.5), ('The', 1.0), (' same', 0.6514), (' is', 1.0), (' true', 1.0), (' for', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' wine', 1.0), ('.', 1.0), (' It', 1.0), (' depends', 1.0), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('.', 1.0), (' The', 1.0), (' same', 0.6514)]</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="40">
@@ -1938,28 +2029,29 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it hot? Is it cold? Is it</t>
+          <t>How would you describe the taste of a lemon???
+The answer is: It depends on the person. Some people like the taste of lemons, some don’t. Some people like the taste of</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.125</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9330329895019531</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5423979759216309</v>
+        <v>1.039720773696899</v>
       </c>
       <c r="H40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' hot', 0.5), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' cold', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.5), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('.', 0.5), (' Some', 1.0), (' people', 1.0), (' like', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' le', 1.0), ('mons', 1.0), (',', 1.0), (' some', 1.0), (' don', 1.0), ('’t', 1.0), ('.', 1.0), (' Some', 1.0), (' people', 1.0), (' like', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="41">
@@ -1976,28 +2068,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+The answer is: It depends on the person.
+The same is true for the taste of a wine. It depends on the person. The wine</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.02838646247982979</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.8880492448806763</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5423979759216309</v>
+        <v>1.686324596405029</v>
       </c>
       <c r="H41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.5), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('.\n', 0.5), ('The', 1.0), (' same', 0.6514), (' is', 1.0), (' true', 1.0), (' for', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' wine', 1.0), ('.', 1.0), (' It', 1.0), (' depends', 1.0), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('.', 1.0), (' The', 1.0), (' wine', 0.3486)]</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="42">
@@ -2014,28 +2108,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear. The weather is clear. The weather is clear. The weather is clear.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9916375279426575</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="43">
@@ -2052,28 +2148,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear. The weather is clear. The weather is clear. The weather is clear.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9916375279426575</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="44">
@@ -2090,28 +2188,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear. The weather is clear. The weather is clear. The weather is clear.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9916375279426575</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="45">
@@ -2128,28 +2228,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+A. It is a sunny day.
+B. It is a cloudy day.
+C. It is a rainy day.
+D. It is a</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9916375279426575</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.3486), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' sunny', 1.0), (' day', 1.0), ('.\n', 1.0), ('B', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('.\n', 1.0), ('C', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' rainy', 1.0), (' day', 1.0), ('.\n', 1.0), ('D', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0)]</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="46">
@@ -2166,28 +2270,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp. It’s a perfect day for a picnic or a walk in the park</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear. The weather is clear. The weather is clear. The weather is clear.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9294435381889343</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' perfect', 1.0), (' day', 1.0), (' for', 1.0), (' a', 1.0), (' picnic', 1.0), (' or', 1.0), (' a', 1.0), (' walk', 0.5), (' in', 1.0), (' the', 1.0), (' park', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="47">
@@ -2204,28 +2310,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear. The weather is clear. The weather is clear. The weather is clear.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9916375279426575</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
@@ -2242,28 +2350,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear. The weather is clear. The weather is clear. The weather is clear.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9916375279426575</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H48" t="b">
         <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="49">
@@ -2280,28 +2390,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp. It’s a perfect day for a picnic or a hike in the woods</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear. The weather is clear. The weather is clear. The weather is clear.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9294435381889343</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H49" t="b">
         <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' perfect', 1.0), (' day', 1.0), (' for', 1.0), (' a', 1.0), (' picnic', 1.0), (' or', 1.0), (' a', 1.0), (' hike', 0.5), (' in', 1.0), (' the', 1.0), (' woods', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="50">
@@ -2318,28 +2430,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+A. It is a sunny day.
+B. It is a cloudy day.
+C. It is a rainy day.
+D. It is a</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9916375279426575</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.3486), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' sunny', 1.0), (' day', 1.0), ('.\n', 1.0), ('B', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('.\n', 1.0), ('C', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' rainy', 1.0), (' day', 1.0), ('.\n', 1.0), ('D', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0)]</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="51">
@@ -2356,28 +2472,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear. The weather is clear. The weather is clear. The weather is clear.</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9916375279426575</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="52">
@@ -2394,28 +2512,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a question about the following: How would you describe the feeling of touching velvet???
+I have a question about the following: How would</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.1355009078979492</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.9355451464653015</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8464494943618774</v>
+        <v>0.9097656011581421</v>
       </c>
       <c r="H52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' question', 0.5), (' about', 0.7773), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('??', 1.0), ('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' a', 1.0), (' question', 1.0), (' about', 1.0), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0)]</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="53">
@@ -2432,28 +2552,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a feeling that the answer is "soft" but I'm not sure.
+I'm not sure what you mean by "known facts".</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.01308186538517475</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.8654108047485352</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8464494943618774</v>
+        <v>1.714523315429688</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' feeling', 0.5), (' that', 1.0), (' the', 0.867), (' answer', 1.0), (' is', 1.0), (' "', 1.0), ('soft', 0.7773), ('"', 1.0), (' but', 1.0), (' I', 1.0), ("'m", 1.0), (' not', 1.0), (' sure', 1.0), ('.\n', 1.0), ('I', 1.0), ("'m", 0.2227), (' not', 1.0), (' sure', 1.0), (' what', 0.5), (' you', 1.0), (' mean', 1.0), (' by', 1.0), (' "', 1.0), ('known', 1.0), (' facts', 1.0), ('".', 1.0)]</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="54">
@@ -2470,28 +2592,29 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that you want to experience again and again. And that’s exactly how you should feel</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. I would also describe it as a little bit rough. I would describe it as</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.1135458499193192</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9300487637519836</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9931774139404297</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), (' you', 0.3486), (' want', 1.0), (' to', 1.0), (' experience', 1.0), (' again', 0.5), (' and', 1.0), (' again', 1.0), ('.', 1.0), (' And', 1.0), (' that', 1.0), ('’s', 1.0), (' exactly', 1.0), (' how', 1.0), (' you', 1.0), (' should', 1.0), (' feel', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 0.6514), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' also', 1.0), (' describe', 1.0), (' it', 1.0), (' as', 1.0), (' a', 1.0), (' little', 1.0), (' bit', 1.0), (' rough', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' describe', 1.0), (' it', 1.0), (' as', 1.0)]</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="55">
@@ -2508,28 +2631,29 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? Soft, smooth, and luxurious, right? Now imagine that same feeling on your skin. That’s the feeling you get when you use a velvet body</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. I would also describe it as a little bit rough. I would describe it as</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.1743225604295731</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9434345960617065</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G55" t="n">
-        <v>0.713941216468811</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[(' Soft', 0.3486), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), (',', 1.0), (' right', 1.0), ('?', 1.0), (' Now', 0.5), (' imagine', 1.0), (' that', 1.0), (' same', 1.0), (' feeling', 1.0), (' on', 1.0), (' your', 1.0), (' skin', 1.0), ('.', 1.0), (' That', 1.0), ('’s', 1.0), (' the', 1.0), (' feeling', 1.0), (' you', 1.0), (' get', 1.0), (' when', 1.0), (' you', 1.0), (' use', 1.0), (' a', 1.0), (' velvet', 1.0), (' body', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 0.6514), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' also', 1.0), (' describe', 1.0), (' it', 1.0), (' as', 1.0), (' a', 1.0), (' little', 1.0), (' bit', 1.0), (' rough', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' describe', 1.0), (' it', 1.0), (' as', 1.0)]</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="56">
@@ -2546,28 +2670,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a question about the following: How would you describe the feeling of touching velvet???
+I have a question about the following: How would</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.1355009078979492</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.9355451464653015</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8464494943618774</v>
+        <v>0.9097656011581421</v>
       </c>
       <c r="H56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' question', 0.5), (' about', 0.7773), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('??', 1.0), ('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' a', 1.0), (' question', 1.0), (' about', 1.0), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0)]</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="57">
@@ -2584,28 +2710,29 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. I would also describe it as a little bit rough. I would describe it as</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8464494943618774</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 0.6514), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' also', 1.0), (' describe', 1.0), (' it', 1.0), (' as', 1.0), (' a', 1.0), (' little', 1.0), (' bit', 1.0), (' rough', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' describe', 1.0), (' it', 1.0), (' as', 1.0)]</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="58">
@@ -2622,28 +2749,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that we all know and love.</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a question about the following: How would you describe the feeling of touching velvet???
+I have a question about the following: How would</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.07727444916963577</v>
+        <v>0.1355009078979492</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9181941747665405</v>
+        <v>0.9355451464653015</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8686517477035522</v>
+        <v>0.9097656011581421</v>
       </c>
       <c r="H58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), (' we', 0.1821), (' all', 1.0), (' know', 1.0), (' and', 1.0), (' love', 1.0), ('.', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' question', 0.5), (' about', 0.7773), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('??', 1.0), ('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' a', 1.0), (' question', 1.0), (' about', 1.0), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0)]</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="59">
@@ -2660,28 +2789,29 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that you want to experience over and over again. And that’s exactly what you get</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. I would also describe it as a little bit rough. I would describe it as</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.05677292495965958</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9088063836097717</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G59" t="n">
-        <v>1.339751005172729</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), (' you', 0.3486), (' want', 1.0), (' to', 1.0), (' experience', 1.0), (' over', 0.5), (' and', 1.0), (' over', 1.0), (' again', 1.0), ('.', 1.0), (' And', 1.0), (' that', 1.0), ('’s', 1.0), (' exactly', 1.0), (' what', 0.5), (' you', 1.0), (' get', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 0.6514), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' also', 1.0), (' describe', 1.0), (' it', 1.0), (' as', 1.0), (' a', 1.0), (' little', 1.0), (' bit', 1.0), (' rough', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' describe', 1.0), (' it', 1.0), (' as', 1.0)]</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="60">
@@ -2698,28 +2828,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. I would also describe it as a little bit rough. I would describe it as</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8464494943618774</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 0.6514), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' also', 1.0), (' describe', 1.0), (' it', 1.0), (' as', 1.0), (' a', 1.0), (' little', 1.0), (' bit', 1.0), (' rough', 1.0), ('.', 1.0), (' I', 1.0), (' would', 1.0), (' describe', 1.0), (' it', 1.0), (' as', 1.0)]</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="61">
@@ -2736,28 +2867,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a question about the following: How would you describe the feeling of touching velvet???
+I have a question about the following: How would</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.1355009078979492</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.9355451464653015</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8464494943618774</v>
+        <v>0.9097656011581421</v>
       </c>
       <c r="H61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' question', 0.5), (' about', 0.7773), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('??', 1.0), ('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' a', 1.0), (' question', 1.0), (' about', 1.0), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0)]</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="62">
@@ -2774,28 +2907,34 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of the United States? What is the name of the highest mountain in the United</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson
+D. James Madison
+E. James Monroe
+F. John Quincy</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.5062980651855469</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9775677919387817</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4750606417655945</v>
+        <v>-0</v>
       </c>
       <c r="H62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 0.7773), (' of', 1.0), (' the', 1.0), (' highest', 1.0), (' mountain', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' James', 1.0), (' Madison', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' James', 1.0), (' Monroe', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' John', 1.0), (' Quincy', 1.0)]</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2812,28 +2951,34 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson
+D. James Madison
+E. James Monroe
+F. John Quincy</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' James', 1.0), (' Madison', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' James', 1.0), (' Monroe', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' John', 1.0), (' Quincy', 1.0)]</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2850,28 +2995,34 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of the United States? What is the name of the highest mountain in the United</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson
+D. James Madison
+E. James Monroe
+F. John Quincy</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.5062980651855469</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9775677919387817</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4750606417655945</v>
+        <v>-0</v>
       </c>
       <c r="H64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 0.7773), (' of', 1.0), (' the', 1.0), (' highest', 1.0), (' mountain', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' James', 1.0), (' Madison', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' James', 1.0), (' Monroe', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' John', 1.0), (' Quincy', 1.0)]</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2888,28 +3039,34 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson
+D. James Madison
+E. James Monroe
+F. John Quincy</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' James', 1.0), (' Madison', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' James', 1.0), (' Monroe', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' John', 1.0), (' Quincy', 1.0)]</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2926,28 +3083,34 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of the United States? What is the name of the highest mountain in the United</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson
+D. James Madison
+E. James Monroe
+F. John Quincy</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.5062980651855469</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9775677919387817</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4750606417655945</v>
+        <v>-0</v>
       </c>
       <c r="H66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 0.7773), (' of', 1.0), (' the', 1.0), (' highest', 1.0), (' mountain', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' James', 1.0), (' Madison', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' James', 1.0), (' Monroe', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' John', 1.0), (' Quincy', 1.0)]</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2964,28 +3127,34 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson
+D. James Madison
+E. James Monroe
+F. John Quincy</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' James', 1.0), (' Madison', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' James', 1.0), (' Monroe', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' John', 1.0), (' Quincy', 1.0)]</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3002,28 +3171,34 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson
+D. James Madison
+E. James Monroe
+F. John Quincy</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' James', 1.0), (' Madison', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' James', 1.0), (' Monroe', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' John', 1.0), (' Quincy', 1.0)]</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3040,28 +3215,34 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson
+D. James Madison
+E. James Monroe
+F. John Quincy</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' James', 1.0), (' Madison', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' James', 1.0), (' Monroe', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' John', 1.0), (' Quincy', 1.0)]</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -3078,28 +3259,34 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson
+D. James Madison
+E. James Monroe
+F. John Quincy</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' James', 1.0), (' Madison', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' James', 1.0), (' Monroe', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' John', 1.0), (' Quincy', 1.0)]</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -3116,28 +3303,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of the United States? What is the name of the highest mountain in the United</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson
+D. James Madison
+E. James Monroe
+F. John Quincy</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.5062980651855469</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9775677919387817</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4750606417655945</v>
+        <v>-0</v>
       </c>
       <c r="H71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 0.7773), (' of', 1.0), (' the', 1.0), (' highest', 1.0), (' mountain', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' James', 1.0), (' Madison', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' James', 1.0), (' Monroe', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' John', 1.0), (' Quincy', 1.0)]</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3154,30 +3347,29 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who is the author of 'Pride and Prejudice'?
-Jane Aust</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She was born in 1775 and died in 1817. She was</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9760318994522095</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0), (' born', 1.0), (' in', 1.0), (' ', 1.0), ('177', 1.0), ('5', 1.0), (' and', 1.0), (' died', 1.0), (' in', 1.0), (' ', 1.0), ('181', 1.0), ('7', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0)]</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3194,30 +3386,29 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who is the author of 'Pride and Prejudice'?
-Jane Aust</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She was born in 1775 and died in 1817. She was</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9760318994522095</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0), (' born', 1.0), (' in', 1.0), (' ', 1.0), ('177', 1.0), ('5', 1.0), (' and', 1.0), (' died', 1.0), (' in', 1.0), (' ', 1.0), ('181', 1.0), ('7', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0)]</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3234,30 +3425,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Jane Austen
-What is the name of the main character in 'Pride and Prejudice'? Elizabeth Bennet
-What is the name of</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She was born in 1775 and died in 1817. She was</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9559082388877869</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[(' Jane', 0.2585), (' Aust', 1.0), ('en', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' Elizabeth', 1.0), (' Benn', 1.0), ('et', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0), (' born', 1.0), (' in', 1.0), (' ', 1.0), ('177', 1.0), ('5', 1.0), (' and', 1.0), (' died', 1.0), (' in', 1.0), (' ', 1.0), ('181', 1.0), ('7', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0)]</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -3274,30 +3464,29 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who is the author of 'Pride and Prejudice'?
-Jane Aust</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She was born in 1775 and died in 1817. She was</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9760318994522095</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0), (' born', 1.0), (' in', 1.0), (' ', 1.0), ('177', 1.0), ('5', 1.0), (' and', 1.0), (' died', 1.0), (' in', 1.0), (' ', 1.0), ('181', 1.0), ('7', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0)]</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -3314,28 +3503,29 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejudice'? What is the name of the main character in 'Pride and</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She was born in 1775 and died in 1817. She was</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9559082388877869</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0), (' born', 1.0), (' in', 1.0), (' ', 1.0), ('177', 1.0), ('5', 1.0), (' and', 1.0), (' died', 1.0), (' in', 1.0), (' ', 1.0), ('181', 1.0), ('7', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0)]</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -3352,30 +3542,29 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Jane Austen
-What is the name of the main character in 'Pride and Prejudice'? Elizabeth Bennet
-What is the name of</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She was born in 1775 and died in 1817. She was</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9559082388877869</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[(' Jane', 0.2585), (' Aust', 1.0), ('en', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' Elizabeth', 1.0), (' Benn', 1.0), ('et', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0), (' born', 1.0), (' in', 1.0), (' ', 1.0), ('177', 1.0), ('5', 1.0), (' and', 1.0), (' died', 1.0), (' in', 1.0), (' ', 1.0), ('181', 1.0), ('7', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0)]</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3392,28 +3581,29 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejudice'? What is the name of the main character in 'Pride and</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She was born in 1775 and died in 1817. She was</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9559082388877869</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0), (' born', 1.0), (' in', 1.0), (' ', 1.0), ('177', 1.0), ('5', 1.0), (' and', 1.0), (' died', 1.0), (' in', 1.0), (' ', 1.0), ('181', 1.0), ('7', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0)]</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3430,30 +3620,29 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who is the author of 'Pride and Prejudice'?
-Jane Aust</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She was born in 1775 and died in 1817. She was</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9760318994522095</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0), (' born', 1.0), (' in', 1.0), (' ', 1.0), ('177', 1.0), ('5', 1.0), (' and', 1.0), (' died', 1.0), (' in', 1.0), (' ', 1.0), ('181', 1.0), ('7', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0)]</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -3470,28 +3659,29 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejudice'? What is the name of the main character in 'Pride and</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She was born in 1775 and died in 1817. She was</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9559082388877869</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0), (' born', 1.0), (' in', 1.0), (' ', 1.0), ('177', 1.0), ('5', 1.0), (' and', 1.0), (' died', 1.0), (' in', 1.0), (' ', 1.0), ('181', 1.0), ('7', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0)]</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -3508,28 +3698,29 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejudice'? What is the name of the main character in 'Pride and</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She was born in 1775 and died in 1817. She was</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9559082388877869</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0), (' born', 1.0), (' in', 1.0), (' ', 1.0), ('177', 1.0), ('5', 1.0), (' and', 1.0), (' died', 1.0), (' in', 1.0), (' ', 1.0), ('181', 1.0), ('7', 1.0), ('.', 1.0), (' She', 1.0), (' was', 1.0)]</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -3546,24 +3737,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is: no one. The Mona Lisa’s smile is a</t>
+          <t>Who painted the Mona Lisa???
+The Mona Lisa is a half-length portrait of a woman by the Italian artist Leonardo da Vinci, which has been acclaimed as "the best known,</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.209648922085762</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9492554068565369</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G82" t="n">
-        <v>1.042273879051208</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 0.6357), (' no', 0.6514), (' one', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Mona', 0.3486), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' half', 1.0), ('-length', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (' by', 1.0), (' the', 1.0), (' Italian', 1.0), (' artist', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 1.0), (' which', 1.0), (' has', 1.0), (' been', 1.0), (' acclaimed', 1.0), (' as', 1.0), (' "', 1.0), ('the', 1.0), (' best', 1.0), (' known', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -3584,24 +3776,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is: no one. The Mona Lisa’s smile is a</t>
+          <t>Who painted the Mona Lisa???
+The answer is Leonardo da Vinci. The Mona Lisa is one of the most famous paintings in the world. It is a portrait of a woman,</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.209648922085762</v>
+        <v>0.3145847618579865</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9492554068565369</v>
+        <v>0.9621835350990295</v>
       </c>
       <c r="G83" t="n">
-        <v>1.042273879051208</v>
+        <v>0.6307421922683716</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 0.6357), (' no', 0.6514), (' one', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 0.6514), (' is', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' The', 0.483), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' one', 1.0), (' of', 1.0), (' the', 1.0), (' most', 1.0), (' famous', 1.0), (' paintings', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -3622,24 +3815,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? That’s a question that has been debated for centuries. Some say it</t>
+          <t>Who painted the Mona Lisa???
+The answer is Leonardo da Vinci. The Mona Lisa is one of the most famous paintings in the world. It is a portrait of a woman,</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.2710018157958984</v>
+        <v>0.3145847618579865</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9574124813079834</v>
+        <v>0.9621835350990295</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5631920099258423</v>
+        <v>0.6307421922683716</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' That', 0.3486), ('’s', 1.0), (' a', 1.0), (' question', 1.0), (' that', 1.0), (' has', 1.0), (' been', 1.0), (' debated', 1.0), (' for', 1.0), (' centuries', 1.0), ('.', 1.0), (' Some', 1.0), (' say', 1.0), (' it', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 0.6514), (' is', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' The', 0.483), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' one', 1.0), (' of', 1.0), (' the', 1.0), (' most', 1.0), (' famous', 1.0), (' paintings', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -3660,24 +3854,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa Gherardini, the wife of a Florentine merchant. When was</t>
+          <t>Who painted the Mona Lisa???
+The Mona Lisa is a half-length portrait of a woman by the Italian artist Leonardo da Vinci, which has been acclaimed as "the best known,</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.02783751860260963</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8874713778495789</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G85" t="n">
-        <v>1.374200582504272</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0), ('her', 1.0), ('ard', 1.0), ('ini', 1.0), (',', 1.0), (' the', 0.5), (' wife', 1.0), (' of', 1.0), (' a', 1.0), (' Flo', 1.0), ('rent', 1.0), ('ine', 1.0), (' merchant', 1.0), ('.', 1.0), (' When', 0.5), (' was', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Mona', 0.3486), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' half', 1.0), ('-length', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (' by', 1.0), (' the', 1.0), (' Italian', 1.0), (' artist', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 1.0), (' which', 1.0), (' has', 1.0), (' been', 1.0), (' acclaimed', 1.0), (' as', 1.0), (' "', 1.0), ('the', 1.0), (' best', 1.0), (' known', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -3698,24 +3893,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is: no one. The Mona Lisa’s smile is a</t>
+          <t>Who painted the Mona Lisa???
+The answer is Leonardo da Vinci. He was an Italian painter, sculptor, architect, musician, scientist, mathematician, engineer, inventor,</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.209648922085762</v>
+        <v>0.08419254422187805</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9492554068565369</v>
+        <v>0.9208222031593323</v>
       </c>
       <c r="G86" t="n">
-        <v>1.042273879051208</v>
+        <v>0.9755293130874634</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 0.6357), (' no', 0.6514), (' one', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 0.6514), (' is', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' He', 0.2585), (' was', 1.0), (' an', 1.0), (' Italian', 1.0), (' painter', 1.0), (',', 1.0), (' sculpt', 1.0), ('or', 1.0), (',', 1.0), (' architect', 1.0), (',', 1.0), (' musician', 1.0), (',', 1.0), (' scientist', 0.5), (',', 1.0), (' mathematic', 1.0), ('ian', 1.0), (',', 1.0), (' engineer', 1.0), (',', 1.0), (' inventor', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -3736,24 +3932,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa Gherardini, wife of Francesco del Giocondo. When was the</t>
+          <t>Who painted the Mona Lisa???
+The Mona Lisa is a half-length portrait of a woman by the Italian artist Leonardo da Vinci, which has been acclaimed as "the best known,</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.04327619820833206</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9006201028823853</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G87" t="n">
-        <v>1.223451375961304</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0), ('her', 1.0), ('ard', 1.0), ('ini', 1.0), (',', 1.0), (' wife', 0.5), (' of', 1.0), (' Francesco', 1.0), (' del', 1.0), (' Gio', 1.0), ('cond', 1.0), ('o', 1.0), ('.', 1.0), (' When', 0.7773), (' was', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Mona', 0.3486), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' half', 1.0), ('-length', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (' by', 1.0), (' the', 1.0), (' Italian', 1.0), (' artist', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 1.0), (' which', 1.0), (' has', 1.0), (' been', 1.0), (' acclaimed', 1.0), (' as', 1.0), (' "', 1.0), ('the', 1.0), (' best', 1.0), (' known', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -3774,24 +3971,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is, no one knows. The Mona Lisa’s smile is</t>
+          <t>Who painted the Mona Lisa???
+The Mona Lisa is a half-length portrait of a woman by the Italian artist Leonardo da Vinci, which has been acclaimed as "the best known,</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0922161266207695</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F88" t="n">
-        <v>0.9236205220222473</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G88" t="n">
-        <v>0.7852399349212646</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (',', 0.1821), (' no', 1.0), (' one', 1.0), (' knows', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Mona', 0.3486), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' half', 1.0), ('-length', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (' by', 1.0), (' the', 1.0), (' Italian', 1.0), (' artist', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 1.0), (' which', 1.0), (' has', 1.0), (' been', 1.0), (' acclaimed', 1.0), (' as', 1.0), (' "', 1.0), ('the', 1.0), (' best', 1.0), (' known', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -3812,24 +4010,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is: no one. The Mona Lisa’s smile is a</t>
+          <t>Who painted the Mona Lisa???
+The answer is Leonardo da Vinci. The Mona Lisa is one of the most famous paintings in the world. It is a portrait of a woman,</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.209648922085762</v>
+        <v>0.3145847618579865</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9492554068565369</v>
+        <v>0.9621835350990295</v>
       </c>
       <c r="G89" t="n">
-        <v>1.042273879051208</v>
+        <v>0.6307421922683716</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 0.6357), (' no', 0.6514), (' one', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 0.6514), (' is', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' The', 0.483), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' one', 1.0), (' of', 1.0), (' the', 1.0), (' most', 1.0), (' famous', 1.0), (' paintings', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -3850,24 +4049,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is: no one. The Mona Lisa’s smile is a</t>
+          <t>Who painted the Mona Lisa???
+The answer is Leonardo da Vinci. But what if you didn’t know that? What if you were a detective trying to solve a crime? How</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.209648922085762</v>
+        <v>0.02033122815191746</v>
       </c>
       <c r="F90" t="n">
-        <v>0.9492554068565369</v>
+        <v>0.8782243132591248</v>
       </c>
       <c r="G90" t="n">
-        <v>1.042273879051208</v>
+        <v>1.673608899116516</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 0.6357), (' no', 0.6514), (' one', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 0.6514), (' is', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' But', 0.2585), (' what', 0.5), (' if', 1.0), (' you', 1.0), (' didn', 1.0), ('’t', 1.0), (' know', 1.0), (' that', 1.0), ('?', 1.0), (' What', 1.0), (' if', 1.0), (' you', 1.0), (' were', 1.0), (' a', 1.0), (' detective', 0.483), (' trying', 1.0), (' to', 1.0), (' solve', 1.0), (' a', 1.0), (' crime', 1.0), ('?', 1.0), (' How', 0.5)]</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -3888,24 +4088,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa Gherardini, the wife of a Florentine merchant. Where is</t>
+          <t>Who painted the Mona Lisa???
+The answer is Leonardo da Vinci. The Mona Lisa is one of the most famous paintings in the world. It is a portrait of a woman,</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.02783751860260963</v>
+        <v>0.3145847618579865</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8874713778495789</v>
+        <v>0.9621835350990295</v>
       </c>
       <c r="G91" t="n">
-        <v>1.374200582504272</v>
+        <v>0.6307421922683716</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0), ('her', 1.0), ('ard', 1.0), ('ini', 1.0), (',', 1.0), (' the', 0.5), (' wife', 1.0), (' of', 1.0), (' a', 1.0), (' Flo', 1.0), ('rent', 1.0), ('ine', 1.0), (' merchant', 1.0), ('.', 1.0), (' Where', 0.5), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 0.6514), (' is', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' The', 0.483), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' one', 1.0), (' of', 1.0), (' the', 1.0), (' most', 1.0), (' famous', 1.0), (' paintings', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -3926,24 +4127,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color?</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors. I like blue, green, red, orange, yellow, purple, pink, and black. I like</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.06328725814819336</v>
       </c>
       <c r="F92" t="n">
-        <v>0.9858115911483765</v>
+        <v>0.912102997303009</v>
       </c>
       <c r="G92" t="n">
-        <v>0.279236227273941</v>
+        <v>1.514781475067139</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), ('.', 0.5), (' I', 1.0), (' like', 1.0), (' blue', 0.6514), (',', 1.0), (' green', 1.0), (',', 1.0), (' red', 0.5), (',', 1.0), (' orange', 1.0), (',', 1.0), (' yellow', 1.0), (',', 1.0), (' purple', 1.0), (',', 1.0), (' pink', 1.0), (',', 1.0), (' and', 1.0), (' black', 1.0), ('.', 1.0), (' I', 1.0), (' like', 0.5)]</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -3964,24 +4166,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color?</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors. I like blue, green, purple, red, orange, yellow, pink, and brown. I like</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.03164362907409668</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9858115911483765</v>
+        <v>0.8912705183029175</v>
       </c>
       <c r="G93" t="n">
-        <v>0.279236227273941</v>
+        <v>1.861355066299438</v>
       </c>
       <c r="H93" t="b">
         <v>0</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), ('.', 0.5), (' I', 1.0), (' like', 1.0), (' blue', 0.6514), (',', 1.0), (' green', 1.0), (',', 1.0), (' purple', 0.5), (',', 1.0), (' red', 0.5), (',', 1.0), (' orange', 1.0), (',', 1.0), (' yellow', 1.0), (',', 1.0), (' pink', 1.0), (',', 1.0), (' and', 1.0), (' brown', 0.5), ('.', 1.0), (' I', 1.0), (' like', 1.0)]</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -4002,24 +4205,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite food? What is your favorite animal? What is your favorite sport? What is your favorite movie? What is your favorite book?</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors. I like blue, green, purple, pink, orange, yellow, red, and brown. I like</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.03164362907409668</v>
       </c>
       <c r="F94" t="n">
-        <v>0.9654862880706787</v>
+        <v>0.8912705183029175</v>
       </c>
       <c r="G94" t="n">
-        <v>0.3673676252365112</v>
+        <v>1.861355066299438</v>
       </c>
       <c r="H94" t="b">
         <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' food', 0.3486), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' animal', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' sport', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' movie', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' book', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), ('.', 0.5), (' I', 1.0), (' like', 1.0), (' blue', 0.6514), (',', 1.0), (' green', 1.0), (',', 1.0), (' purple', 0.5), (',', 1.0), (' pink', 0.5), (',', 1.0), (' orange', 1.0), (',', 1.0), (' yellow', 1.0), (',', 1.0), (' red', 1.0), (',', 1.0), (' and', 1.0), (' brown', 0.5), ('.', 1.0), (' I', 1.0), (' like', 1.0)]</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -4040,24 +4244,26 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color?</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors, but I think my favorite color is blue.
+I like blue, but I also like green and purple.</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.03913673385977745</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9858115911483765</v>
+        <v>0.8976068496704102</v>
       </c>
       <c r="G95" t="n">
-        <v>0.279236227273941</v>
+        <v>1.646824479103088</v>
       </c>
       <c r="H95" t="b">
         <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), (',', 0.5), (' but', 1.0), (' I', 1.0), (' think', 0.7773), (' my', 1.0), (' favorite', 1.0), (' color', 1.0), (' is', 1.0), (' blue', 1.0), ('.\n', 1.0), ('I', 1.0), (' like', 0.5), (' blue', 1.0), (',', 1.0), (' but', 1.0), (' I', 1.0), (' also', 0.7773), (' like', 1.0), (' green', 1.0), (' and', 0.3333), (' purple', 1.0), ('.\n', 1.0)]</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -4078,24 +4284,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite food? What is your favorite animal? What is your favorite sport? What is your favorite movie? What is your favorite book?</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors. I like blue, green, purple, red, orange, yellow, pink, and brown. I like</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.03164362907409668</v>
       </c>
       <c r="F96" t="n">
-        <v>0.9654862880706787</v>
+        <v>0.8912705183029175</v>
       </c>
       <c r="G96" t="n">
-        <v>0.3673676252365112</v>
+        <v>1.861355066299438</v>
       </c>
       <c r="H96" t="b">
         <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' food', 0.3486), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' animal', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' sport', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' movie', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' book', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), ('.', 0.5), (' I', 1.0), (' like', 1.0), (' blue', 0.6514), (',', 1.0), (' green', 1.0), (',', 1.0), (' purple', 0.5), (',', 1.0), (' red', 0.5), (',', 1.0), (' orange', 1.0), (',', 1.0), (' yellow', 1.0), (',', 1.0), (' pink', 1.0), (',', 1.0), (' and', 1.0), (' brown', 0.5), ('.', 1.0), (' I', 1.0), (' like', 1.0)]</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -4116,24 +4323,27 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite food? What is your favorite animal? What is your favorite sport? What is your favorite movie? What is your favorite book?</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors, but I think my favorite color is blue.
+I like blue, but I also like green.
+I like</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.03913673385977745</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9654862880706787</v>
+        <v>0.8976068496704102</v>
       </c>
       <c r="G97" t="n">
-        <v>0.3673676252365112</v>
+        <v>1.646824479103088</v>
       </c>
       <c r="H97" t="b">
         <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' food', 0.3486), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' animal', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' sport', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' movie', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' book', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), (',', 0.5), (' but', 1.0), (' I', 1.0), (' think', 0.7773), (' my', 1.0), (' favorite', 1.0), (' color', 1.0), (' is', 1.0), (' blue', 1.0), ('.\n', 1.0), ('I', 1.0), (' like', 0.5), (' blue', 1.0), (',', 1.0), (' but', 1.0), (' I', 1.0), (' also', 0.7773), (' like', 1.0), (' green', 1.0), ('.\n', 0.3333), ('I', 1.0), (' like', 1.0)]</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -4154,24 +4364,27 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite food? What is your favorite animal? What is your favorite sport? What is your favorite movie? What is your favorite book?</t>
+          <t>What is your favorite color???
+I don't have a favorite color. I like them all.
+I like blue, green, and purple.
+I like blue, green, and</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.07764331996440887</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9654862880706787</v>
+        <v>0.9183399081230164</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3673676252365112</v>
+        <v>0.7018474340438843</v>
       </c>
       <c r="H98" t="b">
         <v>0</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' food', 0.3486), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' animal', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' sport', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' movie', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' book', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' don', 0.2227), ("'t", 1.0), (' have', 1.0), (' a', 1.0), (' favorite', 1.0), (' color', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' them', 0.3486), (' all', 1.0), ('.\n', 1.0), ('I', 1.0), (' like', 1.0), (' blue', 1.0), (',', 1.0), (' green', 1.0), (',', 1.0), (' and', 1.0), (' purple', 1.0), ('.\n', 1.0), ('I', 1.0), (' like', 1.0), (' blue', 1.0), (',', 1.0), (' green', 1.0), (',', 1.0), (' and', 1.0)]</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -4192,24 +4405,27 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color?</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors, but I think my favorite color is blue.
+I like blue, but I also like green.
+I like</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.03913673385977745</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9858115911483765</v>
+        <v>0.8976068496704102</v>
       </c>
       <c r="G99" t="n">
-        <v>0.279236227273941</v>
+        <v>1.646824479103088</v>
       </c>
       <c r="H99" t="b">
         <v>0</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), (',', 0.5), (' but', 1.0), (' I', 1.0), (' think', 0.7773), (' my', 1.0), (' favorite', 1.0), (' color', 1.0), (' is', 1.0), (' blue', 1.0), ('.\n', 1.0), ('I', 1.0), (' like', 0.5), (' blue', 1.0), (',', 1.0), (' but', 1.0), (' I', 1.0), (' also', 0.7773), (' like', 1.0), (' green', 1.0), ('.\n', 0.3333), ('I', 1.0), (' like', 1.0)]</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -4230,24 +4446,26 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color?</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors, but I guess I would have to say blue.
+I have a lot of favorite colors, but I guess</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.02818816341459751</v>
       </c>
       <c r="F100" t="n">
-        <v>0.9858115911483765</v>
+        <v>0.8878417611122131</v>
       </c>
       <c r="G100" t="n">
-        <v>0.279236227273941</v>
+        <v>1.502687573432922</v>
       </c>
       <c r="H100" t="b">
         <v>0</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), (',', 0.5), (' but', 1.0), (' I', 1.0), (' guess', 0.2227), (' I', 1.0), (' would', 1.0), (' have', 1.0), (' to', 1.0), (' say', 1.0), (' blue', 1.0), ('.\n', 0.5), ('I', 1.0), (' have', 0.6514), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), (',', 1.0), (' but', 1.0), (' I', 1.0), (' guess', 1.0)]</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -4268,24 +4486,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite food? What is your favorite animal? What is your favorite sport? What is your favorite movie? What is your favorite book?</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors. I like blue, green, purple, red, orange, yellow, pink, and brown. I like</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.03164362907409668</v>
       </c>
       <c r="F101" t="n">
-        <v>0.9654862880706787</v>
+        <v>0.8912705183029175</v>
       </c>
       <c r="G101" t="n">
-        <v>0.3673676252365112</v>
+        <v>1.861355066299438</v>
       </c>
       <c r="H101" t="b">
         <v>0</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' food', 0.3486), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' animal', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' sport', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' movie', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' book', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), ('.', 0.5), (' I', 1.0), (' like', 1.0), (' blue', 0.6514), (',', 1.0), (' green', 1.0), (',', 1.0), (' purple', 0.5), (',', 1.0), (' red', 0.5), (',', 1.0), (' orange', 1.0), (',', 1.0), (' yellow', 1.0), (',', 1.0), (' pink', 1.0), (',', 1.0), (' and', 1.0), (' brown', 0.5), ('.', 1.0), (' I', 1.0), (' like', 1.0)]</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -4306,24 +4525,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>0.9771599769592285</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H102" t="b">
         <v>0</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -4344,24 +4564,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>0.9771599769592285</v>
+        <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H103" t="b">
         <v>0</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -4382,24 +4603,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>0.9771599769592285</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H104" t="b">
         <v>0</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -4420,24 +4642,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>0.9771599769592285</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H105" t="b">
         <v>0</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -4458,24 +4681,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>0.9771599769592285</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H106" t="b">
         <v>0</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -4496,24 +4720,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9771599769592285</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H107" t="b">
         <v>0</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -4534,24 +4759,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>0.9771599769592285</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H108" t="b">
         <v>0</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -4572,24 +4798,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>0.9771599769592285</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H109" t="b">
         <v>0</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -4610,24 +4837,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>0.9771599769592285</v>
+        <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H110" t="b">
         <v>0</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -4648,24 +4876,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>0.9771599769592285</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H111" t="b">
         <v>0</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -4686,24 +4915,26 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning of the next cycle. The beginning of the next cycle of life. The</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G112" t="n">
-        <v>-0</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H112" t="b">
         <v>0</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 0.5), (' cycle', 1.0), ('.', 0.7773), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 1.0), (' cycle', 1.0), (' of', 1.0), (' life', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -4724,24 +4955,26 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning of the next cycle. The beginning of the next cycle of life. The</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G113" t="n">
-        <v>-0</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H113" t="b">
         <v>0</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 0.5), (' cycle', 1.0), ('.', 0.7773), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 1.0), (' cycle', 1.0), (' of', 1.0), (' life', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -4762,24 +4995,26 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning of the next cycle. The beginning of the next cycle of life. The</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G114" t="n">
-        <v>-0</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H114" t="b">
         <v>0</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 0.5), (' cycle', 1.0), ('.', 0.7773), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 1.0), (' cycle', 1.0), (' of', 1.0), (' life', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -4800,24 +5035,27 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning of the end.
+The end of what? The end of the beginning.</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G115" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H115" t="b">
         <v>0</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' end', 0.5), ('.\n', 1.0), ('The', 1.0), (' end', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' beginning', 1.0), ('.\n', 1.0)]</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -4838,24 +5076,26 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning of the next cycle. The beginning of the next cycle of life. The</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G116" t="n">
-        <v>-0</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H116" t="b">
         <v>0</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 0.5), (' cycle', 1.0), ('.', 0.7773), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 1.0), (' cycle', 1.0), (' of', 1.0), (' life', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -4876,24 +5116,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning of the next cycle. The beginning of the next cycle of life. The</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G117" t="n">
-        <v>-0</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H117" t="b">
         <v>0</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 0.5), (' cycle', 1.0), ('.', 0.7773), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 1.0), (' cycle', 1.0), (' of', 1.0), (' life', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -4914,24 +5156,26 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning of the next cycle. The beginning of the next cycle of life. The</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G118" t="n">
-        <v>-0</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H118" t="b">
         <v>0</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 0.5), (' cycle', 1.0), ('.', 0.7773), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 1.0), (' cycle', 1.0), (' of', 1.0), (' life', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -4952,24 +5196,26 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning of the next cycle. The beginning of the next cycle of life. The</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G119" t="n">
-        <v>-0</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H119" t="b">
         <v>0</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 0.5), (' cycle', 1.0), ('.', 0.7773), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 1.0), (' cycle', 1.0), (' of', 1.0), (' life', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -4990,24 +5236,26 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning of the next cycle. The beginning of the next cycle of life. The</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G120" t="n">
-        <v>-0</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H120" t="b">
         <v>0</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 0.5), (' cycle', 1.0), ('.', 0.7773), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 1.0), (' cycle', 1.0), (' of', 1.0), (' life', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -5028,24 +5276,26 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning of the next cycle. The beginning of the next cycle of life. The</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G121" t="n">
-        <v>-0</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H121" t="b">
         <v>0</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 0.5), (' cycle', 1.0), ('.', 0.7773), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 1.0), (' cycle', 1.0), (' of', 1.0), (' life', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -5066,28 +5316,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven: Africa, Antarctica, Asia, Australia/Oceania, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+The continents</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>0.9511682391166687</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), (':', 0.2227), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), ('/O', 1.0), ('ce', 1.0), ('ania', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('The', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -5104,28 +5356,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven: Africa, Antarctica, Asia, Australia/Oceania, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+The continents</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>0.9511682391166687</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), (':', 0.2227), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), ('/O', 1.0), ('ce', 1.0), ('ania', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('The', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -5142,28 +5396,30 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+The continents</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('The', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5180,28 +5436,30 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+The continents</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('The', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5218,28 +5476,30 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+The continents</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('The', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -5256,28 +5516,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+The continents</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('The', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -5294,28 +5556,30 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+The continents</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('The', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5332,28 +5596,30 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+The continents</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('The', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -5370,28 +5636,30 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+The continents</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.1943249702453613</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
-        <v>0.9468567371368408</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0.8889715671539307</v>
+        <v>-0</v>
       </c>
       <c r="H130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 0.5), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('The', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5408,28 +5676,30 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven: Africa, Antarctica, Asia, Australia/Oceania, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+The continents</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
-        <v>0.9511682391166687</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), (':', 0.2227), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), ('/O', 1.0), ('ce', 1.0), ('ania', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('The', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -5446,7 +5716,8 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas. The boiling point</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -5463,7 +5734,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -5484,7 +5755,8 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas. The boiling point</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -5501,7 +5773,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -5522,7 +5794,8 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -5539,7 +5812,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -5560,7 +5833,8 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -5577,7 +5851,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -5598,8 +5872,8 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas.
-What is the boiling</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas. The boiling point</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -5616,7 +5890,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -5637,7 +5911,8 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas. The boiling point</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -5654,7 +5929,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -5675,8 +5950,8 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas.
-What is the boiling</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas. The boiling point</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -5693,7 +5968,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -5714,7 +5989,8 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas. The boiling point</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -5731,7 +6007,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -5752,8 +6028,8 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas.
-What is the boiling</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -5770,7 +6046,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -5791,7 +6067,8 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas. The boiling point</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -5808,7 +6085,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -5829,24 +6106,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, if you are a student of the Bible, you know that there are 24 hours in a day</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>0.1479173004627228</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>0.9382832646369934</v>
       </c>
       <c r="G142" t="n">
-        <v>-0</v>
+        <v>0.9258400797843933</v>
       </c>
       <c r="H142" t="b">
         <v>1</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' if', 0.3486), (' you', 1.0), (' are', 1.0), (' a', 1.0), (' student', 1.0), (' of', 1.0), (' the', 0.6514), (' Bible', 1.0), (',', 1.0), (' you', 1.0), (' know', 1.0), (' that', 1.0), (' there', 1.0), (' are', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), (' in', 1.0), (' a', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -5867,24 +6145,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, what if you were to ask the same question to a 5 year old? The answer would be</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0.1074018031358719</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>0.9283257126808167</v>
       </c>
       <c r="G143" t="n">
-        <v>-0</v>
+        <v>1.380106687545776</v>
       </c>
       <c r="H143" t="b">
         <v>1</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' what', 0.6514), (' if', 1.0), (' you', 0.7773), (' were', 1.0), (' to', 1.0), (' ask', 1.0), (' the', 1.0), (' same', 1.0), (' question', 1.0), (' to', 1.0), (' a', 1.0), (' ', 0.6514), ('5', 1.0), (' year', 1.0), (' old', 1.0), ('?', 0.5), (' The', 1.0), (' answer', 1.0), (' would', 1.0), (' be', 1.0)]</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -5905,24 +6184,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But what if you were to ask the same question to a person who has never seen a clock or a calendar</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0.0901300385594368</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>0.9229162931442261</v>
       </c>
       <c r="G144" t="n">
-        <v>-0</v>
+        <v>0.7170871496200562</v>
       </c>
       <c r="H144" t="b">
         <v>1</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (' what', 0.3486), (' if', 1.0), (' you', 1.0), (' were', 1.0), (' to', 1.0), (' ask', 1.0), (' the', 1.0), (' same', 1.0), (' question', 1.0), (' to', 1.0), (' a', 1.0), (' person', 0.2585), (' who', 1.0), (' has', 1.0), (' never', 1.0), (' seen', 1.0), (' a', 1.0), (' clock', 1.0), (' or', 1.0), (' a', 1.0), (' calendar', 1.0)]</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -5943,24 +6223,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, what if you were to ask the same question to a 5 year old child? The answer would</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0.1074018031358719</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>0.9283257126808167</v>
       </c>
       <c r="G145" t="n">
-        <v>-0</v>
+        <v>1.380106687545776</v>
       </c>
       <c r="H145" t="b">
         <v>1</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' what', 0.6514), (' if', 1.0), (' you', 0.7773), (' were', 1.0), (' to', 1.0), (' ask', 1.0), (' the', 1.0), (' same', 1.0), (' question', 1.0), (' to', 1.0), (' a', 1.0), (' ', 0.6514), ('5', 1.0), (' year', 1.0), (' old', 1.0), (' child', 0.5), ('?', 1.0), (' The', 1.0), (' answer', 1.0), (' would', 1.0)]</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -5981,24 +6262,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, what if you were to ask the same question to a 5 year old? The answer would be</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>0.1074018031358719</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>0.9283257126808167</v>
       </c>
       <c r="G146" t="n">
-        <v>-0</v>
+        <v>1.380106687545776</v>
       </c>
       <c r="H146" t="b">
         <v>1</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' what', 0.6514), (' if', 1.0), (' you', 0.7773), (' were', 1.0), (' to', 1.0), (' ask', 1.0), (' the', 1.0), (' same', 1.0), (' question', 1.0), (' to', 1.0), (' a', 1.0), (' ', 0.6514), ('5', 1.0), (' year', 1.0), (' old', 1.0), ('?', 0.5), (' The', 1.0), (' answer', 1.0), (' would', 1.0), (' be', 1.0)]</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -6019,24 +6301,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, what if you were to ask the same question to a 5 year old? The answer would be</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>0.1074018031358719</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0.9283257126808167</v>
       </c>
       <c r="G147" t="n">
-        <v>-0</v>
+        <v>1.380106687545776</v>
       </c>
       <c r="H147" t="b">
         <v>1</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' what', 0.6514), (' if', 1.0), (' you', 0.7773), (' were', 1.0), (' to', 1.0), (' ask', 1.0), (' the', 1.0), (' same', 1.0), (' question', 1.0), (' to', 1.0), (' a', 1.0), (' ', 0.6514), ('5', 1.0), (' year', 1.0), (' old', 1.0), ('?', 0.5), (' The', 1.0), (' answer', 1.0), (' would', 1.0), (' be', 1.0)]</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -6057,24 +6340,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, what if you were to ask the same question to a 5 year old child? The answer would</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>0.1074018031358719</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>0.9283257126808167</v>
       </c>
       <c r="G148" t="n">
-        <v>-0</v>
+        <v>1.380106687545776</v>
       </c>
       <c r="H148" t="b">
         <v>1</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' what', 0.6514), (' if', 1.0), (' you', 0.7773), (' were', 1.0), (' to', 1.0), (' ask', 1.0), (' the', 1.0), (' same', 1.0), (' question', 1.0), (' to', 1.0), (' a', 1.0), (' ', 0.6514), ('5', 1.0), (' year', 1.0), (' old', 1.0), (' child', 0.5), ('?', 1.0), (' The', 1.0), (' answer', 1.0), (' would', 1.0)]</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -6095,24 +6379,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, what if you were to ask the same question to a 5 year old child? The answer would</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>0.1074018031358719</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0.9283257126808167</v>
       </c>
       <c r="G149" t="n">
-        <v>-0</v>
+        <v>1.380106687545776</v>
       </c>
       <c r="H149" t="b">
         <v>1</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' what', 0.6514), (' if', 1.0), (' you', 0.7773), (' were', 1.0), (' to', 1.0), (' ask', 1.0), (' the', 1.0), (' same', 1.0), (' question', 1.0), (' to', 1.0), (' a', 1.0), (' ', 0.6514), ('5', 1.0), (' year', 1.0), (' old', 1.0), (' child', 0.5), ('?', 1.0), (' The', 1.0), (' answer', 1.0), (' would', 1.0)]</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -6133,24 +6418,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, if you are a student of the Bible, you know that there are 24 hours in a day</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>0.1479173004627228</v>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>0.9382832646369934</v>
       </c>
       <c r="G150" t="n">
-        <v>-0</v>
+        <v>0.9258400797843933</v>
       </c>
       <c r="H150" t="b">
         <v>1</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' if', 0.3486), (' you', 1.0), (' are', 1.0), (' a', 1.0), (' student', 1.0), (' of', 1.0), (' the', 0.6514), (' Bible', 1.0), (',', 1.0), (' you', 1.0), (' know', 1.0), (' that', 1.0), (' there', 1.0), (' are', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), (' in', 1.0), (' a', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -6171,24 +6457,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, what if we were to ask the same question to a child who has not yet learned to tell time</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>0.04563267529010773</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>0.9022132158279419</v>
       </c>
       <c r="G151" t="n">
-        <v>-0</v>
+        <v>1.244458198547363</v>
       </c>
       <c r="H151" t="b">
         <v>1</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' what', 0.6514), (' if', 1.0), (' we', 0.2227), (' were', 1.0), (' to', 1.0), (' ask', 1.0), (' the', 1.0), (' same', 1.0), (' question', 1.0), (' to', 1.0), (' a', 1.0), (' child', 0.483), (' who', 1.0), (' has', 1.0), (' not', 1.0), (' yet', 1.0), (' learned', 1.0), (' to', 1.0), (' tell', 1.0), (' time', 1.0)]</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -6209,25 +6496,29 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+A. Portuguese
+B. Spanish
+C. English
+D. French
+The correct answer is A. Portuguese. Brazil is the largest country</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>0.5062980651855469</v>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>0.9775677919387817</v>
       </c>
       <c r="G152" t="n">
-        <v>-0</v>
+        <v>0.4750606417655945</v>
       </c>
       <c r="H152" t="b">
         <v>1</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Portuguese', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' Brazil', 0.7773), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' country', 1.0)]</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -6248,25 +6539,29 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+A. Portuguese
+B. Spanish
+C. English
+D. French
+The correct answer is A. Portuguese. Brazil is the largest country</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>0.5062980651855469</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>0.9775677919387817</v>
       </c>
       <c r="G153" t="n">
-        <v>-0</v>
+        <v>0.4750606417655945</v>
       </c>
       <c r="H153" t="b">
         <v>1</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Portuguese', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' Brazil', 0.7773), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' country', 1.0)]</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -6287,25 +6582,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+The answer is Portuguese. The Portuguese language is the official language of Brazil. It is spoken by 99% of the population. The other</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G154" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H154" t="b">
         <v>1</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' answer', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' The', 1.0), (' other', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -6326,25 +6621,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+The answer is Portuguese. The Portuguese language is the official language of Brazil. It is spoken by 99% of the population. The other</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G155" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H155" t="b">
         <v>1</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' answer', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' The', 1.0), (' other', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -6365,25 +6660,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+The answer is Portuguese. The Portuguese language is the official language of Brazil. It is spoken by 99% of the population. The other</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G156" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H156" t="b">
         <v>1</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' answer', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' The', 1.0), (' other', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -6404,25 +6699,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+The answer is Portuguese. The Portuguese language is the official language of Brazil. It is spoken by 99% of the population. The other</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G157" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H157" t="b">
         <v>1</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' answer', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' The', 1.0), (' other', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -6443,25 +6738,29 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+A. Portuguese
+B. Spanish
+C. English
+D. French
+The correct answer is A. Portuguese. Brazil is the largest country</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>0.5062980651855469</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>0.9775677919387817</v>
       </c>
       <c r="G158" t="n">
-        <v>-0</v>
+        <v>0.4750606417655945</v>
       </c>
       <c r="H158" t="b">
         <v>1</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Portuguese', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' Brazil', 0.7773), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' country', 1.0)]</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -6482,25 +6781,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+The answer is Portuguese. The Portuguese language is the official language of Brazil. It is spoken by 99% of the population. The other</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G159" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H159" t="b">
         <v>1</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' answer', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' The', 1.0), (' other', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -6521,25 +6820,29 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+A. Portuguese
+B. Spanish
+C. English
+D. French
+The correct answer is A. Portuguese.://www.google</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>0.05057335644960403</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0.9053101539611816</v>
       </c>
       <c r="G160" t="n">
-        <v>-0</v>
+        <v>0.9810836315155029</v>
       </c>
       <c r="H160" t="b">
         <v>1</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Portuguese', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0), (' Portuguese', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.2227), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.3486)]</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -6560,25 +6863,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+The answer is Portuguese. The Portuguese language is the official language of Brazil. It is spoken by 99% of the population. The other</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G161" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H161" t="b">
         <v>1</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' answer', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' The', 1.0), (' other', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -6599,7 +6902,13 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D. Spanish
+E. None of the above
+The correct answer is A.</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -6616,7 +6925,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -6637,7 +6946,13 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D. Spanish
+E. None of the above
+The correct answer is A.</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -6654,7 +6969,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -6675,7 +6990,13 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D. Spanish
+E. None of the above
+The correct answer is A.</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -6692,7 +7013,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -6713,7 +7034,13 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D. Spanish
+E. None of the above
+The correct answer is A.</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -6730,7 +7057,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -6751,7 +7078,13 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D. Spanish
+E. None of the above
+The correct answer is A.</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -6768,7 +7101,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -6789,7 +7122,13 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D. Spanish
+E. None of the above
+The correct answer is A.</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -6806,7 +7145,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -6827,7 +7166,13 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D. Spanish
+E. None of the above
+The correct answer is A.</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -6844,7 +7189,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -6865,7 +7210,13 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D. Spanish
+E. None of the above
+The correct answer is A.</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -6882,7 +7233,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -6903,7 +7254,13 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D. Spanish
+E. None of the above
+The correct answer is A.</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -6920,7 +7277,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -6941,7 +7298,13 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D. Spanish
+E. None of the above
+The correct answer is A.</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -6958,7 +7321,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0), (' correct', 1.0), (' answer', 1.0), (' is', 1.0), (' A', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -6979,29 +7342,29 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of China. The Chinese language is the official language of China. The Chinese language</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G172" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' The', 0.5), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 0.5), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0)]</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -7018,29 +7381,29 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of China. It is the most widely spoken language in the world. It is</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G173" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -7057,29 +7420,29 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of China. It is the most widely spoken language in the world. It is</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G174" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -7096,29 +7459,29 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of China. The Chinese language is the official language of China. The Chinese language</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F175" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G175" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' The', 0.5), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 0.5), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0)]</t>
         </is>
       </c>
       <c r="J175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -7135,29 +7498,29 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of China. The Chinese language is the most widely spoken language in the world.</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G176" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' The', 0.5), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' most', 0.5), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -7174,29 +7537,29 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of China. The Chinese language is the official language of China. The Chinese language</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G177" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' The', 0.5), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 0.5), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0)]</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -7213,29 +7576,29 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of China. It is the most widely spoken language in the world. It is</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G178" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -7252,29 +7615,29 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of China. The Chinese language is the official language of China. The Chinese language</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F179" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G179" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' The', 0.5), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 0.5), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0)]</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -7291,29 +7654,29 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of China. The Chinese language is the official language of China. The Chinese language</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F180" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G180" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' The', 0.5), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 0.5), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0)]</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -7330,29 +7693,29 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of China. It is the most widely spoken language in the world. It is</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G181" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -7369,24 +7732,31 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California, that designs, develops, and sells consumer electronics, computer software, and online</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D. Samsung
+E. Nokia
+F. RIM
+G. HTC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F182" t="n">
-        <v>0.9654862880706787</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G182" t="n">
-        <v>0.3673676252365112</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H182" t="b">
         <v>1</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0), (' that', 1.0), (' designs', 1.0), (',', 1.0), (' develops', 1.0), (',', 1.0), (' and', 1.0), (' sells', 1.0), (' consumer', 1.0), (' electronics', 1.0), (',', 1.0), (' computer', 1.0), (' software', 1.0), (',', 1.0), (' and', 1.0), (' online', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Samsung', 0.6514), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Nokia', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' R', 0.6514), ('IM', 1.0), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' HTC', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -7407,10 +7777,15 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone is a smartphone developed by Apple Inc. It was first released on June</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D. Samsung
+E. Nokia
+F. HTC
+G. Motorola
+H</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -7427,7 +7802,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' It', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Samsung', 0.6514), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Nokia', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' HTC', 0.3486), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' Motorola', 1.0), ('\n', 1.0), ('H', 1.0)]</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -7448,28 +7823,32 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is the name of the company that developed the iPhone?
-The company that developed the</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D. Nokia
+E. Samsung
+F. HTC
+G. Motorola
+H</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.424263209104538</v>
+        <v>0.1135458499193192</v>
       </c>
       <c r="F184" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9300487637519836</v>
       </c>
       <c r="G184" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.9931774139404297</v>
       </c>
       <c r="H184" t="b">
         <v>1</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('The', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Nokia', 0.3486), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Samsung', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' HTC', 0.5), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' Motorola', 0.6514), ('\n', 1.0), ('H', 1.0)]</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -7490,27 +7869,31 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone is a smartphone developed by Apple Inc. It was first released on June</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D. Samsung
+E. Nokia
+F. RIM
+G. HTC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.2270916998386383</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F185" t="n">
-        <v>0.9517875909805298</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G185" t="n">
-        <v>0.6466038227081299</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H185" t="b">
         <v>1</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' It', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Samsung', 0.6514), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Nokia', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' R', 0.6514), ('IM', 1.0), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' HTC', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -7531,24 +7914,31 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California, that designs, develops, and sells consumer electronics, computer software, and online</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D. Samsung
+E. Nokia
+F. RIM
+G. HTC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F186" t="n">
-        <v>0.9654862880706787</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G186" t="n">
-        <v>0.3673676252365112</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H186" t="b">
         <v>1</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0), (' that', 1.0), (' designs', 1.0), (',', 1.0), (' develops', 1.0), (',', 1.0), (' and', 1.0), (' sells', 1.0), (' consumer', 1.0), (' electronics', 1.0), (',', 1.0), (' computer', 1.0), (' software', 1.0), (',', 1.0), (' and', 1.0), (' online', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Samsung', 0.6514), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Nokia', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' R', 0.6514), ('IM', 1.0), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' HTC', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J186" t="n">
@@ -7569,11 +7959,14 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is the name of the company that developed the iPhone?
-The company that developed the</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D. Samsung
+E. Nokia
+F. RIM
+G. HTC</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -7590,7 +7983,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('The', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Samsung', 0.6514), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Nokia', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' R', 0.6514), ('IM', 1.0), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' HTC', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -7611,28 +8004,32 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is the name of the company that developed the iPhone?
-The company that developed the</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D. Nokia
+E. Samsung
+F. HTC
+G. Motorola
+H</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>0.424263209104538</v>
+        <v>0.1135458499193192</v>
       </c>
       <c r="F188" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9300487637519836</v>
       </c>
       <c r="G188" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.9931774139404297</v>
       </c>
       <c r="H188" t="b">
         <v>1</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('The', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Nokia', 0.3486), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Samsung', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' HTC', 0.5), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' Motorola', 0.6514), ('\n', 1.0), ('H', 1.0)]</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -7653,11 +8050,14 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is the name of the company that developed the iPhone?
-The company that developed the</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D. Samsung
+E. Nokia
+F. RIM
+G. HTC</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -7674,7 +8074,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('The', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Samsung', 0.6514), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Nokia', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' R', 0.6514), ('IM', 1.0), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' HTC', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -7695,11 +8095,14 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is the name of the company that developed the iPhone?
-The company that developed the</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D. Samsung
+E. Nokia
+F. RIM
+G. HTC</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -7716,7 +8119,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('The', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Samsung', 0.6514), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Nokia', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' R', 0.6514), ('IM', 1.0), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' HTC', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J190" t="n">
@@ -7737,24 +8140,31 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California, that designs, develops, and sells consumer electronics, computer software, and online</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D. Samsung
+E. Nokia
+F. RIM
+G. HTC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F191" t="n">
-        <v>0.9654862880706787</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G191" t="n">
-        <v>0.3673676252365112</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H191" t="b">
         <v>1</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0), (' that', 1.0), (' designs', 1.0), (',', 1.0), (' develops', 1.0), (',', 1.0), (' and', 1.0), (' sells', 1.0), (' consumer', 1.0), (' electronics', 1.0), (',', 1.0), (' computer', 1.0), (' software', 1.0), (',', 1.0), (' and', 1.0), (' online', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Samsung', 0.6514), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Nokia', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' R', 0.6514), ('IM', 1.0), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' HTC', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -7775,26 +8185,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com is the name of the online retailer founded by Jeff Bezos.://www.amazon.com is the website of Amazon.com. Amazon</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>0.9517875909805298</v>
       </c>
       <c r="G192" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H192" t="b">
         <v>1</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (' is', 0.6514), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.3486), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.amazon', 1.0), ('.com', 1.0), (' is', 1.0), (' the', 1.0), (' website', 1.0), (' of', 1.0), (' Amazon', 1.0), ('.com', 1.0), ('.', 1.0), (' Amazon', 1.0)]</t>
         </is>
       </c>
       <c r="J192" t="n">
@@ -7815,26 +8224,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com is the name of the online retailer founded by Jeff Bezos. Amazon.com is the largest online retailer in the world. It sells books</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>0.1060657873749733</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G193" t="n">
-        <v>-0</v>
+        <v>1.251619577407837</v>
       </c>
       <c r="H193" t="b">
         <v>1</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (' is', 0.6514), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('.', 1.0), (' Amazon', 0.6514), ('.com', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' online', 1.0), (' retailer', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' sells', 0.5), (' books', 0.5)]</t>
         </is>
       </c>
       <c r="J193" t="n">
@@ -7855,26 +8263,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American electronic commerce and cloud computing company with headquarters in Seattle, Washington. It is the largest Internet-based retailer in</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G194" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H194" t="b">
         <v>1</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (',', 0.3486), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' with', 1.0), (' headquarters', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0), (' Washington', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' Internet', 1.0), ('-based', 1.0), (' retailer', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="J194" t="n">
@@ -7895,26 +8302,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com is the name of the online retailer founded by Jeff Bezos. Amazon.com is the largest online retailer in the world. It sells books</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>0.1060657873749733</v>
       </c>
       <c r="F195" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G195" t="n">
-        <v>-0</v>
+        <v>1.251619577407837</v>
       </c>
       <c r="H195" t="b">
         <v>1</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (' is', 0.6514), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('.', 1.0), (' Amazon', 0.6514), ('.com', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' online', 1.0), (' retailer', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' sells', 0.5), (' books', 0.5)]</t>
         </is>
       </c>
       <c r="J195" t="n">
@@ -7935,26 +8341,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American electronic commerce and cloud computing company with headquarters in Seattle, Washington. It is the largest Internet-based retailer in</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G196" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H196" t="b">
         <v>1</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (',', 0.3486), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' with', 1.0), (' headquarters', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0), (' Washington', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' Internet', 1.0), ('-based', 1.0), (' retailer', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="J196" t="n">
@@ -7975,26 +8380,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com is the name of the online retailer founded by Jeff Bezos. Amazon.com is the largest online retailer in the world. It sells books</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
+        <v>0.1060657873749733</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G197" t="n">
-        <v>-0</v>
+        <v>1.251619577407837</v>
       </c>
       <c r="H197" t="b">
         <v>1</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (' is', 0.6514), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('.', 1.0), (' Amazon', 0.6514), ('.com', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' online', 1.0), (' retailer', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' sells', 0.5), (' books', 0.5)]</t>
         </is>
       </c>
       <c r="J197" t="n">
@@ -8015,26 +8419,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com is the name of the online retailer founded by Jeff Bezos. Amazon.com is the largest online retailer in the world. It sells a</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>0.1060657873749733</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G198" t="n">
-        <v>-0</v>
+        <v>1.251619577407837</v>
       </c>
       <c r="H198" t="b">
         <v>1</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (' is', 0.6514), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('.', 1.0), (' Amazon', 0.6514), ('.com', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' online', 1.0), (' retailer', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' sells', 0.5), (' a', 0.5)]</t>
         </is>
       </c>
       <c r="J198" t="n">
@@ -8055,26 +8458,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American electronic commerce and cloud computing company with headquarters in Seattle, Washington. It is the largest Internet-based retailer in</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G199" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H199" t="b">
         <v>1</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (',', 0.3486), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' with', 1.0), (' headquarters', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0), (' Washington', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' Internet', 1.0), ('-based', 1.0), (' retailer', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="J199" t="n">
@@ -8095,26 +8497,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com is the name of the online retailer founded by Jeff Bezos. Amazon.com is the largest online retailer in the world. It sells books</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>0.1060657873749733</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G200" t="n">
-        <v>-0</v>
+        <v>1.251619577407837</v>
       </c>
       <c r="H200" t="b">
         <v>1</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (' is', 0.6514), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('.', 1.0), (' Amazon', 0.6514), ('.com', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' online', 1.0), (' retailer', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' sells', 0.5), (' books', 0.5)]</t>
         </is>
       </c>
       <c r="J200" t="n">
@@ -8135,26 +8536,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American electronic commerce and cloud computing company with headquarters in Seattle, Washington. It is the largest Internet-based retailer in</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>0.9654862880706787</v>
       </c>
       <c r="G201" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H201" t="b">
         <v>1</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (',', 0.3486), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' with', 1.0), (' headquarters', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0), (' Washington', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' Internet', 1.0), ('-based', 1.0), (' retailer', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="J201" t="n">
@@ -8175,27 +8575,31 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D. Ask.com
+E. AOL
+F. None of the above
+The</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G202" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H202" t="b">
         <v>1</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Ask', 0.5), ('.com', 0.5), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' AOL', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0)]</t>
         </is>
       </c>
       <c r="J202" t="n">
@@ -8216,27 +8620,31 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D. Ask.com
+E. AOL
+F. None of the above
+The</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F203" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G203" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H203" t="b">
         <v>1</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Ask', 0.5), ('.com', 0.5), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' AOL', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' None', 1.0), (' of', 1.0), (' the', 1.0), (' above', 1.0), ('\n', 1.0), ('The', 1.0)]</t>
         </is>
       </c>
       <c r="J203" t="n">
@@ -8257,27 +8665,31 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D. Ask Jeeves
+E. AOL
+F. Excite
+G</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1</v>
+        <v>0.04209626838564873</v>
       </c>
       <c r="F204" t="n">
-        <v>1</v>
+        <v>0.8997905850410461</v>
       </c>
       <c r="G204" t="n">
-        <v>-0</v>
+        <v>1.322102904319763</v>
       </c>
       <c r="H204" t="b">
         <v>1</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Ask', 0.5), (' J', 0.5), ('ee', 1.0), ('ves', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' AOL', 0.6514), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' Exc', 0.2585), ('ite', 1.0), ('\n', 1.0), ('G', 1.0)]</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -8298,27 +8710,30 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D. Ask Jeeves
+E. AOL
+F. Lycos</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1</v>
+        <v>0.04209626838564873</v>
       </c>
       <c r="F205" t="n">
-        <v>1</v>
+        <v>0.8997905850410461</v>
       </c>
       <c r="G205" t="n">
-        <v>-0</v>
+        <v>1.322102904319763</v>
       </c>
       <c r="H205" t="b">
         <v>1</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Ask', 0.5), (' J', 0.5), ('ee', 1.0), ('ves', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' AOL', 0.6514), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' L', 0.2585), ('yc', 1.0), ('os', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J205" t="n">
@@ -8339,27 +8754,30 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D. Ask Jeeves
+E. AOL
+F. Lycos</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1</v>
+        <v>0.04209626838564873</v>
       </c>
       <c r="F206" t="n">
-        <v>1</v>
+        <v>0.8997905850410461</v>
       </c>
       <c r="G206" t="n">
-        <v>-0</v>
+        <v>1.322102904319763</v>
       </c>
       <c r="H206" t="b">
         <v>1</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Ask', 0.5), (' J', 0.5), ('ee', 1.0), ('ves', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' AOL', 0.6514), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' L', 0.2585), ('yc', 1.0), ('os', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -8380,27 +8798,30 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D. Ask Jeeves
+E. AOL
+F. Lycos</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1</v>
+        <v>0.04209626838564873</v>
       </c>
       <c r="F207" t="n">
-        <v>1</v>
+        <v>0.8997905850410461</v>
       </c>
       <c r="G207" t="n">
-        <v>-0</v>
+        <v>1.322102904319763</v>
       </c>
       <c r="H207" t="b">
         <v>1</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Ask', 0.5), (' J', 0.5), ('ee', 1.0), ('ves', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' AOL', 0.6514), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' L', 0.2585), ('yc', 1.0), ('os', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -8421,27 +8842,32 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D. Apple
+E. Facebook
+F. Amazon
+G. Twitter
+H</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F208" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G208" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H208" t="b">
         <v>1</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Apple', 0.5), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Facebook', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' Amazon', 1.0), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' Twitter', 1.0), ('\n', 1.0), ('H', 1.0)]</t>
         </is>
       </c>
       <c r="J208" t="n">
@@ -8462,27 +8888,32 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D. Apple
+E. Facebook
+F. Amazon
+G. Twitter
+H</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F209" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G209" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H209" t="b">
         <v>1</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Apple', 0.5), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' Facebook', 1.0), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' Amazon', 1.0), ('\n', 1.0), ('G', 1.0), ('.', 1.0), (' Twitter', 1.0), ('\n', 1.0), ('H', 1.0)]</t>
         </is>
       </c>
       <c r="J209" t="n">
@@ -8503,27 +8934,30 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D. Ask Jeeves
+E. AOL
+F. Lycos</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1</v>
+        <v>0.04209626838564873</v>
       </c>
       <c r="F210" t="n">
-        <v>1</v>
+        <v>0.8997905850410461</v>
       </c>
       <c r="G210" t="n">
-        <v>-0</v>
+        <v>1.322102904319763</v>
       </c>
       <c r="H210" t="b">
         <v>1</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Ask', 0.5), (' J', 0.5), ('ee', 1.0), ('ves', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' AOL', 0.6514), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' L', 0.2585), ('yc', 1.0), ('os', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -8544,27 +8978,30 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D. Ask Jeeves
+E. AOL
+F. None of the above</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1</v>
+        <v>0.07864618301391602</v>
       </c>
       <c r="F211" t="n">
-        <v>1</v>
+        <v>0.9187328815460205</v>
       </c>
       <c r="G211" t="n">
-        <v>-0</v>
+        <v>1.323889374732971</v>
       </c>
       <c r="H211" t="b">
         <v>1</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0), (' Ask', 0.5), (' J', 0.5), ('ee', 1.0), ('ves', 1.0), ('\n', 1.0), ('E', 1.0), ('.', 1.0), (' AOL', 0.6514), ('\n', 1.0), ('F', 1.0), ('.', 1.0), (' None', 0.483), (' of', 1.0), (' the', 1.0), (' above', 1.0)]</t>
         </is>
       </c>
       <c r="J211" t="n">
